--- a/public/upload-template.xlsx
+++ b/public/upload-template.xlsx
@@ -233,7 +233,7 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>신규촬영 / 일부 수정 / 재사용 중 선택</t>
+        <t>신규촬영 / 일부 수정 / 재사용 / 타기관 임대 중 선택</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -688,7 +688,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>신규촬영 / 일부 수정 / 재사용 (목록에서 선택). 평가 구분과는 별개입니다 — 재평가라도 새로 찍으면 신규촬영</t>
+          <t>신규촬영 / 일부 수정 / 재사용 / 타기관 임대 (목록에서 선택). 평가 구분과는 별개입니다 — 재평가라도 새로 찍으면 신규촬영. 다른 기관(숭실·에듀업 등) 콘텐츠를 받아 쓰면 타기관 임대</t>
         </is>
       </c>
     </row>
@@ -5434,8 +5434,8 @@
     <dataValidation sqref="E2:E202" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="평가 구분" error="신규 또는 재평가 중에서 고르세요." type="list">
       <formula1>"신규,재평가"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F202" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="제작 상태" error="신규촬영 / 일부 수정 / 재사용 중에서 고르세요." type="list">
-      <formula1>"신규촬영,일부 수정,재사용"</formula1>
+    <dataValidation sqref="F2:F202" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="제작 상태" error="신규촬영 / 일부 수정 / 재사용 / 타기관 임대 중에서 고르세요." type="list">
+      <formula1>"신규촬영,일부 수정,재사용,타기관 임대"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G202" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="총 차시" error="1~40 사이 숫자로 입력하세요. 일반 과목은 26입니다." type="whole" operator="between">
       <formula1>1</formula1>
